--- a/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Gas consumption: Germany, France, Spain, Portugal, Denmark (TSO data) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -441,6 +442,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Germany gas consumption by class (Trading Hub Europe) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -604,7 +606,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>France gas consumption by sector (ODRE) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>France gas consumption by sector (ODRE) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -634,12 +637,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - France'!$A$2:$A$69</f>
+              <f>'Chart - France'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - France'!$B$2:$B$69</f>
+              <f>'Chart - France'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -662,12 +665,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - France'!$A$2:$A$69</f>
+              <f>'Chart - France'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - France'!$C$2:$C$69</f>
+              <f>'Chart - France'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -1193,7 +1196,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-05 05:03 UTC; 2104 days, 2021-01-01 to 2026-10-05</t>
+          <t>2026-10-08 08:14 UTC; 2107 days, 2021-01-01 to 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2512,10 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>40.29927</v>
+        <v>40.32403</v>
+      </c>
+      <c r="C70" t="n">
+        <v>5.88948</v>
       </c>
       <c r="D70" t="n">
         <v>18.84825</v>
@@ -3210,10 +3216,10 @@
         <v>46266</v>
       </c>
       <c r="B61" t="n">
-        <v>8.93651</v>
+        <v>8.93652</v>
       </c>
       <c r="C61" t="n">
-        <v>31.36279</v>
+        <v>31.38753</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +3234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3997,6 +4003,17 @@
       </c>
       <c r="C69" t="n">
         <v>4.23821</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3.74529</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2.14419</v>
       </c>
     </row>
   </sheetData>
@@ -4011,7 +4028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2105"/>
+  <dimension ref="A1:P2108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103503,8 +103520,17 @@
       <c r="D2089" t="n">
         <v>1104.01</v>
       </c>
+      <c r="E2089" t="n">
+        <v>216.08</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>133.87</v>
+      </c>
       <c r="G2089" t="n">
-        <v>1.43</v>
+        <v>2.87</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>349.95</v>
       </c>
       <c r="I2089" t="n">
         <v>654.0599999999999</v>
@@ -103544,8 +103570,17 @@
       <c r="D2090" t="n">
         <v>1129.9</v>
       </c>
+      <c r="E2090" t="n">
+        <v>236.62</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>130.57</v>
+      </c>
       <c r="G2090" t="n">
-        <v>24.93</v>
+        <v>49.86</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>367.19</v>
       </c>
       <c r="I2090" t="n">
         <v>638.52</v>
@@ -103580,13 +103615,22 @@
         <v>368.44</v>
       </c>
       <c r="C2091" t="n">
-        <v>1141.47</v>
+        <v>1141.48</v>
       </c>
       <c r="D2091" t="n">
-        <v>1509.91</v>
+        <v>1509.92</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>314.15</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>199.2</v>
       </c>
       <c r="G2091" t="n">
-        <v>90.84</v>
+        <v>181.68</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>513.35</v>
       </c>
       <c r="I2091" t="n">
         <v>836.16</v>
@@ -103621,13 +103665,22 @@
         <v>419.23</v>
       </c>
       <c r="C2092" t="n">
-        <v>1271.4</v>
+        <v>1271.7</v>
       </c>
       <c r="D2092" t="n">
-        <v>1690.63</v>
+        <v>1690.94</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>323.33</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>207.42</v>
       </c>
       <c r="G2092" t="n">
-        <v>91</v>
+        <v>181.99</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>530.75</v>
       </c>
       <c r="I2092" t="n">
         <v>898.8</v>
@@ -103662,13 +103715,22 @@
         <v>431.03</v>
       </c>
       <c r="C2093" t="n">
-        <v>1206.61</v>
+        <v>1206.83</v>
       </c>
       <c r="D2093" t="n">
-        <v>1637.63</v>
+        <v>1637.86</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>208.49</v>
       </c>
       <c r="G2093" t="n">
-        <v>95.95999999999999</v>
+        <v>191.91</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>537</v>
       </c>
       <c r="J2093" t="n">
         <v>42.18</v>
@@ -103700,13 +103762,22 @@
         <v>456.75</v>
       </c>
       <c r="C2094" t="n">
-        <v>1227.92</v>
+        <v>1227.9</v>
       </c>
       <c r="D2094" t="n">
-        <v>1684.67</v>
+        <v>1684.65</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>208.26</v>
       </c>
       <c r="G2094" t="n">
-        <v>112.17</v>
+        <v>224.35</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>563.52</v>
       </c>
       <c r="J2094" t="n">
         <v>42.59</v>
@@ -103738,13 +103809,22 @@
         <v>472</v>
       </c>
       <c r="C2095" t="n">
-        <v>1148.66</v>
+        <v>1169.36</v>
       </c>
       <c r="D2095" t="n">
-        <v>1620.66</v>
+        <v>1641.35</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>358.62</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>190.72</v>
       </c>
       <c r="G2095" t="n">
-        <v>119.18</v>
+        <v>238.36</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>549.34</v>
       </c>
       <c r="J2095" t="n">
         <v>39.37</v>
@@ -103776,13 +103856,22 @@
         <v>412.19</v>
       </c>
       <c r="C2096" t="n">
-        <v>954.86</v>
+        <v>955.24</v>
       </c>
       <c r="D2096" t="n">
-        <v>1367.05</v>
+        <v>1367.43</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>307.48</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>136.7</v>
       </c>
       <c r="G2096" t="n">
-        <v>79.38</v>
+        <v>158.75</v>
+      </c>
+      <c r="H2096" t="n">
+        <v>444.18</v>
       </c>
       <c r="J2096" t="n">
         <v>33.26</v>
@@ -103814,13 +103903,22 @@
         <v>341.5</v>
       </c>
       <c r="C2097" t="n">
-        <v>897.9299999999999</v>
+        <v>898.59</v>
       </c>
       <c r="D2097" t="n">
-        <v>1239.43</v>
+        <v>1240.08</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>272.02</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>131.72</v>
       </c>
       <c r="G2097" t="n">
-        <v>47.92</v>
+        <v>95.84</v>
+      </c>
+      <c r="H2097" t="n">
+        <v>403.74</v>
       </c>
       <c r="J2097" t="n">
         <v>33.93</v>
@@ -103849,16 +103947,25 @@
         <v>46293</v>
       </c>
       <c r="B2098" t="n">
-        <v>296.38</v>
+        <v>296.39</v>
       </c>
       <c r="C2098" t="n">
-        <v>1198.01</v>
+        <v>1198.15</v>
       </c>
       <c r="D2098" t="n">
-        <v>1494.39</v>
+        <v>1494.54</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>197.08</v>
       </c>
       <c r="G2098" t="n">
-        <v>128.77</v>
+        <v>257.54</v>
+      </c>
+      <c r="H2098" t="n">
+        <v>565.41</v>
       </c>
       <c r="J2098" t="n">
         <v>43.36</v>
@@ -103890,13 +103997,22 @@
         <v>270.49</v>
       </c>
       <c r="C2099" t="n">
-        <v>1080.92</v>
+        <v>1080.91</v>
       </c>
       <c r="D2099" t="n">
-        <v>1351.41</v>
+        <v>1351.4</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>300.19</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>198.36</v>
       </c>
       <c r="G2099" t="n">
-        <v>68.33</v>
+        <v>136.66</v>
+      </c>
+      <c r="H2099" t="n">
+        <v>498.55</v>
       </c>
       <c r="J2099" t="n">
         <v>43.09</v>
@@ -103928,13 +104044,22 @@
         <v>261.67</v>
       </c>
       <c r="C2100" t="n">
-        <v>1079.9</v>
+        <v>1082.26</v>
       </c>
       <c r="D2100" t="n">
-        <v>1341.57</v>
+        <v>1343.94</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>364.7</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>201.8</v>
       </c>
       <c r="G2100" t="n">
-        <v>122.71</v>
+        <v>245.4</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>566.5</v>
       </c>
       <c r="J2100" t="n">
         <v>43.08</v>
@@ -103966,10 +104091,10 @@
         <v>275.55</v>
       </c>
       <c r="C2101" t="n">
-        <v>1207.22</v>
+        <v>1213.33</v>
       </c>
       <c r="D2101" t="n">
-        <v>1482.77</v>
+        <v>1488.88</v>
       </c>
       <c r="G2101" t="n">
         <v>157.15</v>
@@ -104004,10 +104129,10 @@
         <v>324.7</v>
       </c>
       <c r="C2102" t="n">
-        <v>1199.19</v>
+        <v>1226.91</v>
       </c>
       <c r="D2102" t="n">
-        <v>1523.89</v>
+        <v>1551.61</v>
       </c>
       <c r="G2102" t="n">
         <v>153.3</v>
@@ -104016,7 +104141,7 @@
         <v>43.53</v>
       </c>
       <c r="K2102" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L2102" t="n">
         <v>76</v>
@@ -104042,10 +104167,10 @@
         <v>352.04</v>
       </c>
       <c r="C2103" t="n">
-        <v>1009.69</v>
+        <v>1010.61</v>
       </c>
       <c r="D2103" t="n">
-        <v>1361.74</v>
+        <v>1362.65</v>
       </c>
       <c r="G2103" t="n">
         <v>108.43</v>
@@ -104079,8 +104204,35 @@
       <c r="B2104" t="n">
         <v>392.28</v>
       </c>
+      <c r="C2104" t="n">
+        <v>990.42</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>1382.69</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>68.54000000000001</v>
+      </c>
       <c r="J2104" t="n">
-        <v>35.38</v>
+        <v>36.83</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>81</v>
+      </c>
+      <c r="L2104" t="n">
+        <v>51</v>
+      </c>
+      <c r="M2104" t="n">
+        <v>29</v>
+      </c>
+      <c r="N2104" t="n">
+        <v>34</v>
+      </c>
+      <c r="O2104" t="n">
+        <v>14</v>
+      </c>
+      <c r="P2104" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="2105">
@@ -104089,6 +104241,111 @@
       </c>
       <c r="B2105" t="n">
         <v>425.86</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>1203.07</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>1628.93</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>90</v>
+      </c>
+      <c r="L2105" t="n">
+        <v>56</v>
+      </c>
+      <c r="M2105" t="n">
+        <v>33</v>
+      </c>
+      <c r="N2105" t="n">
+        <v>37</v>
+      </c>
+      <c r="O2105" t="n">
+        <v>15</v>
+      </c>
+      <c r="P2105" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>431.93</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>1463.83</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>1895.76</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>159.21</v>
+      </c>
+      <c r="J2106" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="K2106" t="n">
+        <v>114</v>
+      </c>
+      <c r="L2106" t="n">
+        <v>70</v>
+      </c>
+      <c r="M2106" t="n">
+        <v>44</v>
+      </c>
+      <c r="N2106" t="n">
+        <v>50</v>
+      </c>
+      <c r="O2106" t="n">
+        <v>16</v>
+      </c>
+      <c r="P2106" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>413.22</v>
+      </c>
+      <c r="J2107" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="K2107" t="n">
+        <v>102</v>
+      </c>
+      <c r="L2107" t="n">
+        <v>73</v>
+      </c>
+      <c r="M2107" t="n">
+        <v>29</v>
+      </c>
+      <c r="N2107" t="n">
+        <v>53</v>
+      </c>
+      <c r="O2107" t="n">
+        <v>17</v>
+      </c>
+      <c r="P2107" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>497.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
@@ -1196,7 +1196,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08 08:14 UTC; 2107 days, 2021-01-01 to 2026-10-08</t>
+          <t>2026-10-08 08:19 UTC; 2107 days, 2021-01-01 to 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
@@ -1196,7 +1196,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08 08:19 UTC; 2107 days, 2021-01-01 to 2026-10-08</t>
+          <t>2026-10-08 08:23 UTC; 2107 days, 2021-01-01 to 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_daily.xlsx
@@ -1196,7 +1196,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08 08:23 UTC; 2107 days, 2021-01-01 to 2026-10-08</t>
+          <t>2026-10-08 08:25 UTC; 2107 days, 2021-01-01 to 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v>5.88948</v>
       </c>
       <c r="D70" t="n">
-        <v>18.84825</v>
+        <v>25.8256</v>
       </c>
       <c r="E70" t="n">
         <v>3.436</v>
@@ -103732,6 +103732,9 @@
       <c r="H2093" t="n">
         <v>537</v>
       </c>
+      <c r="I2093" t="n">
+        <v>927.54</v>
+      </c>
       <c r="J2093" t="n">
         <v>42.18</v>
       </c>
@@ -103779,6 +103782,9 @@
       <c r="H2094" t="n">
         <v>563.52</v>
       </c>
+      <c r="I2094" t="n">
+        <v>970.87</v>
+      </c>
       <c r="J2094" t="n">
         <v>42.59</v>
       </c>
@@ -103826,6 +103832,9 @@
       <c r="H2095" t="n">
         <v>549.34</v>
       </c>
+      <c r="I2095" t="n">
+        <v>885.0700000000001</v>
+      </c>
       <c r="J2095" t="n">
         <v>39.37</v>
       </c>
@@ -103873,6 +103882,9 @@
       <c r="H2096" t="n">
         <v>444.18</v>
       </c>
+      <c r="I2096" t="n">
+        <v>706.9400000000001</v>
+      </c>
       <c r="J2096" t="n">
         <v>33.26</v>
       </c>
@@ -103920,6 +103932,9 @@
       <c r="H2097" t="n">
         <v>403.74</v>
       </c>
+      <c r="I2097" t="n">
+        <v>681.64</v>
+      </c>
       <c r="J2097" t="n">
         <v>33.93</v>
       </c>
@@ -103967,6 +103982,9 @@
       <c r="H2098" t="n">
         <v>565.41</v>
       </c>
+      <c r="I2098" t="n">
+        <v>972.49</v>
+      </c>
       <c r="J2098" t="n">
         <v>43.36</v>
       </c>
@@ -104014,6 +104032,9 @@
       <c r="H2099" t="n">
         <v>498.55</v>
       </c>
+      <c r="I2099" t="n">
+        <v>837.9299999999999</v>
+      </c>
       <c r="J2099" t="n">
         <v>43.09</v>
       </c>
@@ -104061,6 +104082,9 @@
       <c r="H2100" t="n">
         <v>566.5</v>
       </c>
+      <c r="I2100" t="n">
+        <v>994.87</v>
+      </c>
       <c r="J2100" t="n">
         <v>43.08</v>
       </c>
@@ -104099,6 +104123,9 @@
       <c r="G2101" t="n">
         <v>157.15</v>
       </c>
+      <c r="I2101" t="n">
+        <v>880.21</v>
+      </c>
       <c r="J2101" t="n">
         <v>50.44</v>
       </c>
@@ -104137,6 +104164,9 @@
       <c r="G2102" t="n">
         <v>153.3</v>
       </c>
+      <c r="I2102" t="n">
+        <v>900.09</v>
+      </c>
       <c r="J2102" t="n">
         <v>43.53</v>
       </c>
@@ -104175,6 +104205,9 @@
       <c r="G2103" t="n">
         <v>108.43</v>
       </c>
+      <c r="I2103" t="n">
+        <v>714.53</v>
+      </c>
       <c r="J2103" t="n">
         <v>37.03</v>
       </c>
@@ -104213,6 +104246,9 @@
       <c r="G2104" t="n">
         <v>68.54000000000001</v>
       </c>
+      <c r="I2104" t="n">
+        <v>697.34</v>
+      </c>
       <c r="J2104" t="n">
         <v>36.83</v>
       </c>
@@ -104251,6 +104287,9 @@
       <c r="G2105" t="n">
         <v>117.65</v>
       </c>
+      <c r="I2105" t="n">
+        <v>915.17</v>
+      </c>
       <c r="J2105" t="n">
         <v>44.6</v>
       </c>
@@ -104288,6 +104327,9 @@
       </c>
       <c r="G2106" t="n">
         <v>159.21</v>
+      </c>
+      <c r="I2106" t="n">
+        <v>1005.46</v>
       </c>
       <c r="J2106" t="n">
         <v>47.83</v>
